--- a/STG.CO.xlsx
+++ b/STG.CO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E82CE1-C347-4867-9FAD-F8B3C5DE5697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E68AC37-E5AF-4060-A057-78A96A5B7EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="195">
   <si>
     <t>Scandivian Tobacco</t>
   </si>
@@ -688,6 +688,9 @@
   </si>
   <si>
     <t>Q426</t>
+  </si>
+  <si>
+    <t>STG.CO</t>
   </si>
 </sst>
 </file>
@@ -1660,7 +1663,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1668,10 +1671,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="6">
-        <v>78.741</v>
+        <v>78.62</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1683,104 +1686,102 @@
       </c>
       <c r="J4" s="6">
         <f>+J2*J3</f>
-        <v>5511.87</v>
+        <v>5629.192</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>194</v>
+      </c>
       <c r="I5" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="6">
-        <v>13.5</v>
+        <v>61.6</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
       <c r="I6" t="s">
         <v>6</v>
       </c>
       <c r="J6" s="6">
-        <f>3520.6+1250</f>
-        <v>4770.6000000000004</v>
+        <f>3690.9+1251</f>
+        <v>4941.8999999999996</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
+      <c r="B7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
       <c r="I7" t="s">
         <v>7</v>
       </c>
       <c r="J7" s="6">
         <f>+J4-J5+J6</f>
-        <v>10268.970000000001</v>
+        <v>10509.491999999998</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F8" s="16"/>
+      <c r="B8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="16"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
+      <c r="F10" s="16"/>
       <c r="I10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B11" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
       <c r="I11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="4" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>11</v>
       </c>
       <c r="I13" t="s">
         <v>51</v>
@@ -1788,7 +1789,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>175</v>
+        <v>11</v>
       </c>
       <c r="I14" s="20">
         <v>10219</v>
@@ -1796,12 +1797,12 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I16" t="s">
         <v>187</v>
@@ -1809,16 +1810,21 @@
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
         <v>188</v>
       </c>
     </row>
@@ -1933,13 +1939,17 @@
       <c r="G3" s="6">
         <v>618.70000000000005</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="6">
+        <v>780</v>
+      </c>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6">
         <v>575</v>
       </c>
-      <c r="L3" s="6"/>
+      <c r="L3" s="6">
+        <v>793</v>
+      </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
@@ -2026,13 +2036,17 @@
       <c r="G4" s="6">
         <v>687.3</v>
       </c>
-      <c r="H4" s="6"/>
+      <c r="H4" s="6">
+        <v>730</v>
+      </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6">
         <v>630</v>
       </c>
-      <c r="L4" s="6"/>
+      <c r="L4" s="6">
+        <v>746</v>
+      </c>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
@@ -2119,13 +2133,17 @@
       <c r="G5" s="6">
         <v>667.7</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="6">
+        <v>851</v>
+      </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6">
         <v>655</v>
       </c>
-      <c r="L5" s="6"/>
+      <c r="L5" s="6">
+        <v>795</v>
+      </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -2218,7 +2236,9 @@
       <c r="K6" s="6">
         <v>660.2</v>
       </c>
-      <c r="L6" s="6"/>
+      <c r="L6" s="6">
+        <v>876</v>
+      </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
@@ -2311,7 +2331,9 @@
       <c r="K7" s="6">
         <v>956.2</v>
       </c>
-      <c r="L7" s="6"/>
+      <c r="L7" s="6">
+        <v>1138</v>
+      </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
@@ -2404,7 +2426,9 @@
       <c r="K8" s="6">
         <v>64</v>
       </c>
-      <c r="L8" s="6"/>
+      <c r="L8" s="6">
+        <v>115</v>
+      </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -2499,7 +2523,9 @@
       <c r="K9" s="6">
         <v>178.8</v>
       </c>
-      <c r="L9" s="6"/>
+      <c r="L9" s="6">
+        <v>205</v>
+      </c>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
@@ -2609,7 +2635,9 @@
       <c r="K10" s="7">
         <v>1859.2</v>
       </c>
-      <c r="L10" s="7"/>
+      <c r="L10" s="7">
+        <v>2334</v>
+      </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -2718,7 +2746,9 @@
       <c r="K11" s="6">
         <v>1035.4000000000001</v>
       </c>
-      <c r="L11" s="6"/>
+      <c r="L11" s="6">
+        <v>1279</v>
+      </c>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
@@ -2834,7 +2864,10 @@
         <f>+K10-K11</f>
         <v>823.8</v>
       </c>
-      <c r="L12" s="6"/>
+      <c r="L12" s="6">
+        <f>+L10-L11</f>
+        <v>1055</v>
+      </c>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
@@ -2952,7 +2985,9 @@
       <c r="K13" s="6">
         <v>232</v>
       </c>
-      <c r="L13" s="6"/>
+      <c r="L13" s="6">
+        <v>248</v>
+      </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
@@ -3061,7 +3096,9 @@
       <c r="K14" s="6">
         <v>302.39999999999998</v>
       </c>
-      <c r="L14" s="6"/>
+      <c r="L14" s="6">
+        <v>340.3</v>
+      </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
@@ -3170,7 +3207,9 @@
       <c r="K15" s="6">
         <v>30.6</v>
       </c>
-      <c r="L15" s="6"/>
+      <c r="L15" s="6">
+        <v>48.6</v>
+      </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
@@ -3286,7 +3325,10 @@
         <f>63.3+64+75.6</f>
         <v>202.89999999999998</v>
       </c>
-      <c r="L16" s="6"/>
+      <c r="L16" s="6">
+        <f>65.5+61.9+59.8</f>
+        <v>187.2</v>
+      </c>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
@@ -3411,7 +3453,10 @@
         <f>+K12-SUM(K13:K14,K16)+K15</f>
         <v>117.1</v>
       </c>
-      <c r="L17" s="6"/>
+      <c r="L17" s="6">
+        <f>+L12-SUM(L13:L14,L16)+L15</f>
+        <v>328.1</v>
+      </c>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
@@ -3529,7 +3574,9 @@
       <c r="K18" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L18" s="6"/>
+      <c r="L18" s="6">
+        <v>6.6</v>
+      </c>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
@@ -3638,7 +3685,9 @@
       <c r="K19" s="6">
         <v>27.3</v>
       </c>
-      <c r="L19" s="6"/>
+      <c r="L19" s="6">
+        <v>31.6</v>
+      </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
@@ -3747,7 +3796,9 @@
       <c r="K20" s="6">
         <v>93</v>
       </c>
-      <c r="L20" s="6"/>
+      <c r="L20" s="6">
+        <v>84.5</v>
+      </c>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -3863,7 +3914,10 @@
         <f>+K17+K18+K19-K20</f>
         <v>56.300000000000011</v>
       </c>
-      <c r="L21" s="6"/>
+      <c r="L21" s="6">
+        <f>+L17+L18+L19-L20</f>
+        <v>281.80000000000007</v>
+      </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
@@ -3981,7 +4035,9 @@
       <c r="K22" s="6">
         <v>12.9</v>
       </c>
-      <c r="L22" s="6"/>
+      <c r="L22" s="6">
+        <v>64.900000000000006</v>
+      </c>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
@@ -4097,7 +4153,10 @@
         <f>+K21-K22</f>
         <v>43.400000000000013</v>
       </c>
-      <c r="L23" s="6"/>
+      <c r="L23" s="6">
+        <f>+L21-L22</f>
+        <v>216.90000000000006</v>
+      </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
@@ -4275,7 +4334,7 @@
         <v>0.65323000038052315</v>
       </c>
       <c r="H25" s="6">
-        <f t="shared" ref="H25:K25" si="10">+H23/H26</f>
+        <f t="shared" ref="H25:L25" si="10">+H23/H26</f>
         <v>2.8787014139876979</v>
       </c>
       <c r="I25" s="6">
@@ -4290,7 +4349,10 @@
         <f t="shared" si="10"/>
         <v>0.55023771790808262</v>
       </c>
-      <c r="L25" s="6"/>
+      <c r="L25" s="6">
+        <f t="shared" si="10"/>
+        <v>2.7588399898244726</v>
+      </c>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
@@ -4407,7 +4469,9 @@
       <c r="K26" s="6">
         <v>78.875</v>
       </c>
-      <c r="L26" s="6"/>
+      <c r="L26" s="6">
+        <v>78.62</v>
+      </c>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -4965,7 +5029,7 @@
       </c>
       <c r="L32" s="22">
         <f t="shared" si="18"/>
-        <v>-1</v>
+        <v>-1.1603286186160799E-2</v>
       </c>
       <c r="M32" s="22">
         <f t="shared" si="18"/>
@@ -5094,9 +5158,9 @@
         <f t="shared" ref="K33:N33" si="21">+K12/K10</f>
         <v>0.44309380378657481</v>
       </c>
-      <c r="L33" s="21" t="e">
+      <c r="L33" s="21">
         <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
+        <v>0.45201371036846616</v>
       </c>
       <c r="M33" s="21" t="e">
         <f t="shared" si="21"/>
@@ -5225,9 +5289,9 @@
         <f t="shared" ref="K34:N34" si="26">+K17/K10</f>
         <v>6.2984079173838206E-2</v>
       </c>
-      <c r="L34" s="21" t="e">
+      <c r="L34" s="21">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
+        <v>0.14057412167952016</v>
       </c>
       <c r="M34" s="21" t="e">
         <f t="shared" si="26"/>
@@ -5356,9 +5420,9 @@
         <f t="shared" ref="K35:N35" si="31">+K22/K21</f>
         <v>0.22912966252220246</v>
       </c>
-      <c r="L35" s="21" t="e">
+      <c r="L35" s="21">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>0.23030518097941799</v>
       </c>
       <c r="M35" s="21" t="e">
         <f t="shared" si="31"/>
@@ -33099,14 +33163,14 @@
       </c>
       <c r="J3" s="26">
         <f>+Main!J2</f>
-        <v>70</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="L3" t="s">
         <v>117</v>
       </c>
       <c r="O3" s="26">
         <f>+J3</f>
-        <v>70</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -33115,14 +33179,14 @@
       </c>
       <c r="E4" s="27">
         <f ca="1">+TODAY()</f>
-        <v>46226</v>
+        <v>46260</v>
       </c>
       <c r="G4" t="s">
         <v>119</v>
       </c>
       <c r="J4" s="28">
         <f ca="1">V62</f>
-        <v>110.50341825100335</v>
+        <v>108.99870635334247</v>
       </c>
       <c r="L4" t="s">
         <v>120</v>
@@ -33144,7 +33208,7 @@
       </c>
       <c r="J5" s="31">
         <f ca="1">J4/J3-1</f>
-        <v>0.57862026072861927</v>
+        <v>0.52232830102433625</v>
       </c>
       <c r="L5" t="s">
         <v>122</v>
@@ -33433,67 +33497,67 @@
       <c r="E24" s="33"/>
       <c r="F24" s="33"/>
       <c r="G24" s="39">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H24" s="39">
         <f>G24+1</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="39">
         <f t="shared" ref="I24:V24" si="0">H24+1</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" s="39">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" s="39">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L24" s="39">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M24" s="39">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" s="39">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O24" s="39">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P24" s="39">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q24" s="39">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R24" s="39">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S24" s="39">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T24" s="39">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U24" s="39">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V24" s="39">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
@@ -34640,43 +34704,43 @@
       <c r="L52" s="57"/>
       <c r="M52" s="57">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>604.06384593461837</v>
+        <v>696.73567148672987</v>
       </c>
       <c r="N52" s="57">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>992.62265278540872</v>
+        <v>984.81219931804981</v>
       </c>
       <c r="O52" s="57">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>919.76961404886447</v>
+        <v>912.53240487268783</v>
       </c>
       <c r="P52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>852.26358732968174</v>
+        <v>845.55754946918773</v>
       </c>
       <c r="Q52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>789.71213137887923</v>
+        <v>783.49827978337589</v>
       </c>
       <c r="R52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>731.75160797492481</v>
+        <v>725.99381888184371</v>
       </c>
       <c r="S52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>678.04506794006807</v>
+        <v>672.70986887216714</v>
       </c>
       <c r="T52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>628.28029231143887</v>
+        <v>623.33666748705366</v>
       </c>
       <c r="U52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>582.16797727940684</v>
+        <v>577.58718730451778</v>
       </c>
       <c r="V52" s="58">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>539.44005234146857</v>
+        <v>535.19546713537864</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -34685,43 +34749,43 @@
       </c>
       <c r="M53" s="74">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.56388888888888888</v>
+        <v>0.65555555555555556</v>
       </c>
       <c r="N53" s="74">
         <f ca="1">M53+1</f>
-        <v>1.5638888888888889</v>
+        <v>1.6555555555555554</v>
       </c>
       <c r="O53" s="74">
         <f ca="1">N53+1</f>
-        <v>2.5638888888888891</v>
+        <v>2.6555555555555554</v>
       </c>
       <c r="P53" s="74">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.5638888888888891</v>
+        <v>3.6555555555555554</v>
       </c>
       <c r="Q53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>4.5638888888888891</v>
+        <v>4.655555555555555</v>
       </c>
       <c r="R53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>5.5638888888888891</v>
+        <v>5.655555555555555</v>
       </c>
       <c r="S53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>6.5638888888888891</v>
+        <v>6.655555555555555</v>
       </c>
       <c r="T53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>7.5638888888888891</v>
+        <v>7.655555555555555</v>
       </c>
       <c r="U53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>8.56388888888889</v>
+        <v>8.655555555555555</v>
       </c>
       <c r="V53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>9.56388888888889</v>
+        <v>9.655555555555555</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -34734,7 +34798,7 @@
       <c r="Q54" s="59"/>
       <c r="V54" s="3">
         <f ca="1">SUM(M52:V52)</f>
-        <v>7318.1168293247592</v>
+        <v>7357.9591146109915</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -34778,7 +34842,7 @@
       <c r="U56" s="61"/>
       <c r="V56" s="62">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>6140.1328271774955</v>
+        <v>6091.8191788887943</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -34806,7 +34870,7 @@
       <c r="U57" s="64"/>
       <c r="V57" s="65">
         <f ca="1">V54+V56</f>
-        <v>13458.249656502256</v>
+        <v>13449.778293499785</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -34819,7 +34883,7 @@
       <c r="Q58" s="59"/>
       <c r="V58" s="66">
         <f>+Main!J5</f>
-        <v>13.5</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.2">
@@ -34847,7 +34911,7 @@
       <c r="U59" s="61"/>
       <c r="V59" s="62">
         <f>+Main!J6</f>
-        <v>4770.6000000000004</v>
+        <v>4941.8999999999996</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.2">
@@ -34860,7 +34924,7 @@
       <c r="Q60" s="59"/>
       <c r="V60" s="66">
         <f ca="1">V57+V58-V59</f>
-        <v>8701.1496565022553</v>
+        <v>8569.4782934997857</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -34888,7 +34952,7 @@
       <c r="U61" s="61"/>
       <c r="V61" s="62">
         <f>+Main!J3</f>
-        <v>78.741</v>
+        <v>78.62</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.2">
@@ -34897,7 +34961,7 @@
       </c>
       <c r="V62" s="66">
         <f ca="1">V60/V61</f>
-        <v>110.50341825100335</v>
+        <v>108.99870635334247</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -34958,7 +35022,7 @@
       </c>
       <c r="C69" s="68">
         <f ca="1">+J4</f>
-        <v>110.50341825100335</v>
+        <v>108.99870635334247</v>
       </c>
       <c r="D69" s="69">
         <v>-5.0000000000000001E-3</v>
@@ -34986,7 +35050,7 @@
       </c>
       <c r="N69" s="68">
         <f ca="1">+J4</f>
-        <v>110.50341825100335</v>
+        <v>108.99870635334247</v>
       </c>
       <c r="O69" s="69">
         <v>0.08</v>
@@ -35017,25 +35081,25 @@
       </c>
       <c r="D70" s="71">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>187.82421948574668</v>
+        <v>186.4839044671948</v>
       </c>
       <c r="E70" s="71">
-        <v>193.70836631488461</v>
+        <v>192.34571373836906</v>
       </c>
       <c r="F70" s="71">
-        <v>200.58902946274534</v>
+        <v>199.20025632595872</v>
       </c>
       <c r="G70" s="72">
-        <v>208.7651638249458</v>
+        <v>207.34535222488861</v>
       </c>
       <c r="H70" s="71">
-        <v>218.66859313959904</v>
+        <v>217.21118587227193</v>
       </c>
       <c r="I70" s="71">
-        <v>230.94705301387512</v>
+        <v>229.44303392377898</v>
       </c>
       <c r="J70" s="71">
-        <v>246.61841368761225</v>
+        <v>245.05490255260545</v>
       </c>
       <c r="M70" s="79"/>
       <c r="N70" s="70">
@@ -35043,25 +35107,25 @@
       </c>
       <c r="O70" s="71">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>202.65506162108613</v>
+        <v>201.25844535692153</v>
       </c>
       <c r="P70" s="71">
-        <v>205.14436251895486</v>
+        <v>203.73829630313034</v>
       </c>
       <c r="Q70" s="71">
-        <v>207.13580323724986</v>
+        <v>205.72217706009738</v>
       </c>
       <c r="R70" s="72">
-        <v>208.7651638249458</v>
+        <v>207.34535222488861</v>
       </c>
       <c r="S70" s="71">
-        <v>210.12296431469238</v>
+        <v>208.69799819554794</v>
       </c>
       <c r="T70" s="71">
-        <v>211.27187242140099</v>
+        <v>209.84254478610583</v>
       </c>
       <c r="U70" s="71">
-        <v>212.2566507985799</v>
+        <v>210.82358472086983</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35070,50 +35134,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="71">
-        <v>153.57882121539748</v>
+        <v>152.17735320715548</v>
       </c>
       <c r="E71" s="71">
-        <v>156.95300884769208</v>
+        <v>155.53583967502715</v>
       </c>
       <c r="F71" s="71">
-        <v>160.7895841552039</v>
+        <v>159.35456218172024</v>
       </c>
       <c r="G71" s="72">
-        <v>165.20414405673716</v>
+        <v>163.74857973694009</v>
       </c>
       <c r="H71" s="71">
-        <v>170.35432071429778</v>
+        <v>168.87479099028502</v>
       </c>
       <c r="I71" s="71">
-        <v>176.46079915469394</v>
+        <v>174.95285405119245</v>
       </c>
       <c r="J71" s="71">
-        <v>183.84234663887088</v>
+        <v>182.30005285551655</v>
       </c>
       <c r="M71" s="79"/>
       <c r="N71" s="70">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="71">
-        <v>160.54971379652849</v>
+        <v>159.11580801584509</v>
       </c>
       <c r="P71" s="71">
-        <v>162.44596316179869</v>
+        <v>161.00323353184675</v>
       </c>
       <c r="Q71" s="71">
-        <v>163.96296265401486</v>
+        <v>162.51317394464809</v>
       </c>
       <c r="R71" s="72">
-        <v>165.20414405673716</v>
+        <v>163.74857973694009</v>
       </c>
       <c r="S71" s="71">
-        <v>166.23846189233907</v>
+        <v>164.77808456385009</v>
       </c>
       <c r="T71" s="71">
-        <v>167.11365390707917</v>
+        <v>165.64920403277395</v>
       </c>
       <c r="U71" s="71">
-        <v>167.86381849114213</v>
+        <v>166.39587786328011</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35122,50 +35186,50 @@
         <v>0.08</v>
       </c>
       <c r="D72" s="72">
-        <v>127.46886127812442</v>
+        <v>126.02186700082873</v>
       </c>
       <c r="E72" s="72">
-        <v>129.41321106191708</v>
+        <v>127.95551954275777</v>
       </c>
       <c r="F72" s="72">
-        <v>131.57183612800529</v>
+        <v>130.10226848726674</v>
       </c>
       <c r="G72" s="72">
-        <v>133.9906526083094</v>
+        <v>132.50777734919416</v>
       </c>
       <c r="H72" s="72">
-        <v>136.72970467534094</v>
+        <v>135.2317599556367</v>
       </c>
       <c r="I72" s="72">
-        <v>139.86905122578167</v>
+        <v>138.35383474272305</v>
       </c>
       <c r="J72" s="72">
-        <v>143.5178634823796</v>
+        <v>141.98257230517427</v>
       </c>
       <c r="M72" s="79"/>
       <c r="N72" s="70">
         <v>0.08</v>
       </c>
       <c r="O72" s="72">
-        <v>130.34074527000183</v>
+        <v>128.87795072985145</v>
       </c>
       <c r="P72" s="72">
-        <v>131.827744555979</v>
+        <v>130.35676898217625</v>
       </c>
       <c r="Q72" s="72">
-        <v>133.01734398476074</v>
+        <v>131.53982358403613</v>
       </c>
       <c r="R72" s="72">
-        <v>133.9906526083094</v>
+        <v>132.50777734919416</v>
       </c>
       <c r="S72" s="72">
-        <v>134.80174312793332</v>
+        <v>133.31440548682588</v>
       </c>
       <c r="T72" s="72">
-        <v>135.48805049069202</v>
+        <v>133.99693698789889</v>
       </c>
       <c r="U72" s="72">
-        <v>136.07631394448518</v>
+        <v>134.58196398881861</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35174,50 +35238,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="71">
-        <v>106.91939803564519</v>
+        <v>105.43741442997556</v>
       </c>
       <c r="E73" s="71">
-        <v>108.01564407783336</v>
+        <v>106.52670855821125</v>
       </c>
       <c r="F73" s="71">
-        <v>109.20452763807445</v>
+        <v>107.70805273779122</v>
       </c>
       <c r="G73" s="72">
-        <v>110.50341825100335</v>
+        <v>108.99870635334247</v>
       </c>
       <c r="H73" s="71">
-        <v>111.9343173271577</v>
+        <v>110.42053129205937</v>
       </c>
       <c r="I73" s="71">
-        <v>113.52551239437145</v>
+        <v>112.00163569462015</v>
       </c>
       <c r="J73" s="71">
-        <v>115.31399483519681</v>
+        <v>113.77877636037344</v>
       </c>
       <c r="M73" s="79"/>
       <c r="N73" s="70">
         <v>0.09</v>
       </c>
       <c r="O73" s="71">
-        <v>107.57921128107466</v>
+        <v>106.09304342777227</v>
       </c>
       <c r="P73" s="71">
-        <v>108.77055486141599</v>
+        <v>107.27683202707865</v>
       </c>
       <c r="Q73" s="71">
-        <v>109.72362972568904</v>
+        <v>108.22386290652378</v>
       </c>
       <c r="R73" s="72">
-        <v>110.50341825100335</v>
+        <v>108.99870635334247</v>
       </c>
       <c r="S73" s="71">
-        <v>111.15324202209861</v>
+        <v>109.6444092256914</v>
       </c>
       <c r="T73" s="71">
-        <v>111.70309290533309</v>
+        <v>110.19077319460207</v>
       </c>
       <c r="U73" s="71">
-        <v>112.1743936623912</v>
+        <v>110.65908516795405</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35226,50 +35290,50 @@
         <v>0.1</v>
       </c>
       <c r="D74" s="71">
-        <v>90.336936582506851</v>
+        <v>88.827367099665864</v>
       </c>
       <c r="E74" s="71">
-        <v>90.916408567787315</v>
+        <v>89.402682502845593</v>
       </c>
       <c r="F74" s="71">
-        <v>91.527088346644717</v>
+        <v>90.00898184450746</v>
       </c>
       <c r="G74" s="72">
-        <v>92.174177218008509</v>
+        <v>90.651429114398454</v>
       </c>
       <c r="H74" s="71">
-        <v>92.864100315850436</v>
+        <v>91.336403358676705</v>
       </c>
       <c r="I74" s="71">
-        <v>93.60488905763512</v>
+        <v>92.071878385039852</v>
       </c>
       <c r="J74" s="71">
-        <v>94.406716572151097</v>
+        <v>92.867954349904807</v>
       </c>
       <c r="M74" s="79"/>
       <c r="N74" s="70">
         <v>0.1</v>
       </c>
       <c r="O74" s="71">
-        <v>89.792277836652133</v>
+        <v>88.286615218770194</v>
       </c>
       <c r="P74" s="71">
-        <v>90.762681288315846</v>
+        <v>89.250057916989121</v>
       </c>
       <c r="Q74" s="71">
-        <v>91.539004049646806</v>
+        <v>90.020812075564237</v>
       </c>
       <c r="R74" s="72">
-        <v>92.174177218008509</v>
+        <v>90.651429114398454</v>
       </c>
       <c r="S74" s="71">
-        <v>92.70348819164326</v>
+        <v>91.17694331342696</v>
       </c>
       <c r="T74" s="71">
-        <v>93.151366707795745</v>
+        <v>91.621609174143387</v>
       </c>
       <c r="U74" s="71">
-        <v>93.535262578783588</v>
+        <v>92.002751340471747</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35278,50 +35342,50 @@
         <v>0.11</v>
       </c>
       <c r="D75" s="71">
-        <v>76.682661715033532</v>
+        <v>75.150880021048991</v>
       </c>
       <c r="E75" s="71">
-        <v>76.942195793966235</v>
+        <v>75.408338780570418</v>
       </c>
       <c r="F75" s="71">
-        <v>77.201729872898952</v>
+        <v>75.665797540091873</v>
       </c>
       <c r="G75" s="72">
-        <v>77.461263951831654</v>
+        <v>75.923256299613314</v>
       </c>
       <c r="H75" s="71">
-        <v>77.720798030764371</v>
+        <v>76.180715059134769</v>
       </c>
       <c r="I75" s="71">
-        <v>77.980332109697059</v>
+        <v>76.43817381865621</v>
       </c>
       <c r="J75" s="71">
-        <v>78.239866188629776</v>
+        <v>76.695632578177666</v>
       </c>
       <c r="M75" s="79"/>
       <c r="N75" s="70">
         <v>0.11</v>
       </c>
       <c r="O75" s="71">
-        <v>75.495293303916398</v>
+        <v>73.973006196238387</v>
       </c>
       <c r="P75" s="71">
-        <v>76.296244308622619</v>
+        <v>74.767552534650378</v>
       </c>
       <c r="Q75" s="71">
-        <v>76.937005112387581</v>
+        <v>75.403189605380007</v>
       </c>
       <c r="R75" s="72">
-        <v>77.461263951831654</v>
+        <v>75.923256299613314</v>
       </c>
       <c r="S75" s="71">
-        <v>77.898146318035046</v>
+        <v>76.356645211474415</v>
       </c>
       <c r="T75" s="71">
-        <v>78.267816012514857</v>
+        <v>76.723358906126137</v>
       </c>
       <c r="U75" s="71">
-        <v>78.5846757506404</v>
+        <v>77.037684930113301</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35330,50 +35394,50 @@
         <v>0.12</v>
       </c>
       <c r="D76" s="71">
-        <v>65.250524604423859</v>
+        <v>63.70053519029765</v>
       </c>
       <c r="E76" s="71">
-        <v>65.310868725065689</v>
+        <v>63.760347585937978</v>
       </c>
       <c r="F76" s="71">
-        <v>65.355747075657447</v>
+        <v>63.804830488874146</v>
       </c>
       <c r="G76" s="72">
-        <v>65.383050687555922</v>
+        <v>63.831893513737377</v>
       </c>
       <c r="H76" s="71">
-        <v>65.39026888380495</v>
+        <v>63.839048106517325</v>
       </c>
       <c r="I76" s="71">
-        <v>65.374388852057109</v>
+        <v>63.823308002401468</v>
       </c>
       <c r="J76" s="71">
-        <v>65.331763503681287</v>
+        <v>63.781058249248318</v>
       </c>
       <c r="M76" s="80"/>
       <c r="N76" s="70">
         <v>0.12</v>
       </c>
       <c r="O76" s="71">
-        <v>63.742715589965364</v>
+        <v>62.206012304495587</v>
       </c>
       <c r="P76" s="71">
-        <v>64.411000259354111</v>
+        <v>62.868408352705195</v>
       </c>
       <c r="Q76" s="71">
-        <v>64.945627994865106</v>
+        <v>63.39832519127291</v>
       </c>
       <c r="R76" s="72">
-        <v>65.383050687555922</v>
+        <v>63.831893513737377</v>
       </c>
       <c r="S76" s="71">
-        <v>65.747569598131591</v>
+        <v>64.193200449124461</v>
       </c>
       <c r="T76" s="71">
-        <v>66.056008676311038</v>
+        <v>64.498921702144287</v>
       </c>
       <c r="U76" s="71">
-        <v>66.320385029036245</v>
+        <v>64.760968490446999</v>
       </c>
     </row>
   </sheetData>
